--- a/salidas/empresas/BA.xlsx
+++ b/salidas/empresas/BA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>48.60414123535156</v>
+        <v>48.60415267944336</v>
       </c>
       <c r="C2" t="n">
         <v>68.30999755859375</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>51.93838882446289</v>
+        <v>51.93840026855469</v>
       </c>
       <c r="C3" t="n">
         <v>72.69000244140625</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>55.68246078491211</v>
+        <v>55.68249130249023</v>
       </c>
       <c r="C4" t="n">
         <v>77.93000030517578</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>59.62663269042969</v>
+        <v>59.62662887573242</v>
       </c>
       <c r="C5" t="n">
         <v>83.44999694824219</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>59.68722915649414</v>
+        <v>59.68720626831055</v>
       </c>
       <c r="C6" t="n">
         <v>83.25</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>58.72649383544922</v>
+        <v>58.72649765014648</v>
       </c>
       <c r="C7" t="n">
         <v>81.91000366210938</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>55.50730514526367</v>
+        <v>55.50732803344727</v>
       </c>
       <c r="C8" t="n">
         <v>77.41999816894531</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>53.90752029418945</v>
+        <v>53.90749740600586</v>
       </c>
       <c r="C9" t="n">
         <v>74.90000152587891</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>56.75043487548828</v>
+        <v>56.75042724609375</v>
       </c>
       <c r="C10" t="n">
         <v>78.84999847412109</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>57.47735595703125</v>
+        <v>57.47734069824219</v>
       </c>
       <c r="C11" t="n">
         <v>79.86000061035156</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>63.94343948364258</v>
+        <v>63.94344711303711</v>
       </c>
       <c r="C12" t="n">
         <v>88.52999877929688</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>64.16738128662109</v>
+        <v>64.16736602783203</v>
       </c>
       <c r="C13" t="n">
         <v>88.83999633789062</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>64.68740081787109</v>
+        <v>64.68744659423828</v>
       </c>
       <c r="C14" t="n">
         <v>89.55999755859375</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>63.26955413818359</v>
+        <v>63.2695426940918</v>
       </c>
       <c r="C15" t="n">
         <v>87.26000213623047</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>64.46591949462891</v>
+        <v>64.46592712402344</v>
       </c>
       <c r="C16" t="n">
         <v>88.91000366210938</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>67.43150329589844</v>
+        <v>67.43147277832031</v>
       </c>
       <c r="C17" t="n">
         <v>93</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>73.20669555664062</v>
+        <v>73.20668792724609</v>
       </c>
       <c r="C18" t="n">
         <v>100.5899963378906</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>69.98269653320312</v>
+        <v>69.98267364501953</v>
       </c>
       <c r="C19" t="n">
         <v>96.16000366210938</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>75.27360534667969</v>
+        <v>75.27359771728516</v>
       </c>
       <c r="C20" t="n">
         <v>103.4300003051758</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>70.61510467529297</v>
+        <v>70.6151123046875</v>
       </c>
       <c r="C21" t="n">
         <v>96.69999694824219</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>76.66887664794922</v>
+        <v>76.66888427734375</v>
       </c>
       <c r="C22" t="n">
         <v>104.9899978637695</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>71.99529266357422</v>
+        <v>71.99526214599609</v>
       </c>
       <c r="C23" t="n">
         <v>98.58999633789062</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>67.82026672363281</v>
+        <v>67.82022857666016</v>
       </c>
       <c r="C24" t="n">
         <v>92.54000091552734</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>64.09722900390625</v>
+        <v>64.09723663330078</v>
       </c>
       <c r="C25" t="n">
         <v>87.45999908447266</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>60.96053314208984</v>
+        <v>60.96051788330078</v>
       </c>
       <c r="C26" t="n">
         <v>83.18000030517578</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>60.97324752807617</v>
+        <v>60.97327423095703</v>
       </c>
       <c r="C27" t="n">
         <v>82.79000091552734</v>
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>62.49775695800781</v>
+        <v>62.49778747558594</v>
       </c>
       <c r="C29" t="n">
         <v>84.86000061035156</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>61.24290084838867</v>
+        <v>61.24287796020508</v>
       </c>
       <c r="C30" t="n">
         <v>82.76999664306641</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>48.62731170654297</v>
+        <v>48.62731552124023</v>
       </c>
       <c r="C31" t="n">
         <v>65.72000122070312</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>45.21630859375</v>
+        <v>45.21631622314453</v>
       </c>
       <c r="C32" t="n">
         <v>61.11000061035156</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>48.80837631225586</v>
+        <v>48.80837249755859</v>
       </c>
       <c r="C33" t="n">
         <v>65.55999755859375</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>42.69615173339844</v>
+        <v>42.69614791870117</v>
       </c>
       <c r="C34" t="n">
         <v>57.34999847412109</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>39.02584838867188</v>
+        <v>39.02584457397461</v>
       </c>
       <c r="C35" t="n">
         <v>52.41999816894531</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>31.97589683532715</v>
+        <v>31.97589302062988</v>
       </c>
       <c r="C36" t="n">
         <v>42.63000106811523</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>32.00588607788086</v>
+        <v>32.00589370727539</v>
       </c>
       <c r="C37" t="n">
         <v>42.66999816894531</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>31.73585891723633</v>
+        <v>31.73586845397949</v>
       </c>
       <c r="C38" t="n">
         <v>42.31000137329102</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>23.82019233703613</v>
+        <v>23.82019424438477</v>
       </c>
       <c r="C39" t="n">
         <v>31.44000053405762</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>26.95681571960449</v>
+        <v>26.95681762695312</v>
       </c>
       <c r="C40" t="n">
         <v>35.58000183105469</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>30.34346580505371</v>
+        <v>30.34347343444824</v>
       </c>
       <c r="C41" t="n">
         <v>40.04999923706055</v>
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>32.51618957519531</v>
+        <v>32.51619338989258</v>
       </c>
       <c r="C43" t="n">
         <v>42.5</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>32.82986450195312</v>
+        <v>32.82987594604492</v>
       </c>
       <c r="C44" t="n">
         <v>42.90999984741211</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>38.36674499511719</v>
+        <v>38.36675262451172</v>
       </c>
       <c r="C45" t="n">
         <v>49.66999816894531</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>41.8272590637207</v>
+        <v>41.82724761962891</v>
       </c>
       <c r="C46" t="n">
         <v>54.15000152587891</v>
@@ -1355,7 +1367,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>40.83981704711914</v>
+        <v>40.83982467651367</v>
       </c>
       <c r="C48" t="n">
         <v>52.40999984741211</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>42.18011093139648</v>
+        <v>42.18012237548828</v>
       </c>
       <c r="C49" t="n">
         <v>54.13000106811523</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>47.22178649902344</v>
+        <v>47.22177505493164</v>
       </c>
       <c r="C50" t="n">
         <v>60.59999847412109</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>49.55263137817383</v>
+        <v>49.5526237487793</v>
       </c>
       <c r="C51" t="n">
         <v>63.15999984741211</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>56.96668243408203</v>
+        <v>56.96667861938477</v>
       </c>
       <c r="C52" t="n">
         <v>72.61000061035156</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>56.82547760009766</v>
+        <v>56.82547378540039</v>
       </c>
       <c r="C53" t="n">
         <v>72.43000030517578</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>50.64509201049805</v>
+        <v>50.64509963989258</v>
       </c>
       <c r="C54" t="n">
         <v>64.18000030517578</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>49.51666259765625</v>
+        <v>49.51667404174805</v>
       </c>
       <c r="C55" t="n">
         <v>62.75</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>53.76997375488281</v>
+        <v>53.76998519897461</v>
       </c>
       <c r="C56" t="n">
         <v>68.13999938964844</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>48.53143310546875</v>
+        <v>48.53142547607422</v>
       </c>
       <c r="C57" t="n">
         <v>61.13000106811523</v>
@@ -1630,7 +1642,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>56.08147048950195</v>
+        <v>56.08146286010742</v>
       </c>
       <c r="C59" t="n">
         <v>70.63999938964844</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>50.93390655517578</v>
+        <v>50.93391418457031</v>
       </c>
       <c r="C60" t="n">
         <v>63.77000045776367</v>
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>52.12398147583008</v>
+        <v>52.12398529052734</v>
       </c>
       <c r="C61" t="n">
         <v>65.26000213623047</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>55.49455642700195</v>
+        <v>55.49456405639648</v>
       </c>
       <c r="C62" t="n">
         <v>69.48000335693359</v>
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>57.84946441650391</v>
+        <v>57.84945297241211</v>
       </c>
       <c r="C63" t="n">
         <v>72.01000213623047</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>59.39189147949219</v>
+        <v>59.39189910888672</v>
       </c>
       <c r="C64" t="n">
         <v>73.93000030517578</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>64.09150695800781</v>
+        <v>64.09149169921875</v>
       </c>
       <c r="C65" t="n">
         <v>79.77999877929688</v>
@@ -1842,7 +1854,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1871,7 +1883,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>56.91128158569336</v>
+        <v>56.91125869750977</v>
       </c>
       <c r="C68" t="n">
         <v>70.47000122070312</v>
@@ -1929,11 +1941,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>54.36210250854492</v>
+        <v>54.36209106445312</v>
       </c>
       <c r="C69" t="n">
         <v>66.86000061035156</v>
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>49.19907760620117</v>
+        <v>49.19906997680664</v>
       </c>
       <c r="C70" t="n">
         <v>60.5099983215332</v>
@@ -1987,11 +1999,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>53.49210357666016</v>
+        <v>53.49211120605469</v>
       </c>
       <c r="C71" t="n">
         <v>65.79000091552734</v>
@@ -2016,11 +2028,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>56.20612716674805</v>
+        <v>56.20613098144531</v>
       </c>
       <c r="C72" t="n">
         <v>68.69000244140625</v>
@@ -2045,11 +2057,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>60.01919174194336</v>
+        <v>60.01921081542969</v>
       </c>
       <c r="C73" t="n">
         <v>73.34999847412109</v>
@@ -2074,11 +2086,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>60.69836807250977</v>
+        <v>60.6983757019043</v>
       </c>
       <c r="C74" t="n">
         <v>74.18000030517578</v>
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>61.68938446044922</v>
+        <v>61.68936920166016</v>
       </c>
       <c r="C75" t="n">
         <v>74.94999694824219</v>
@@ -2132,11 +2144,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>61.21199035644531</v>
+        <v>61.21197509765625</v>
       </c>
       <c r="C76" t="n">
         <v>74.37000274658203</v>
@@ -2161,11 +2173,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>63.21207046508789</v>
+        <v>63.21207427978516</v>
       </c>
       <c r="C77" t="n">
         <v>76.80000305175781</v>
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>57.63046646118164</v>
+        <v>57.63045501708984</v>
       </c>
       <c r="C78" t="n">
         <v>69.61000061035156</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>61.51332473754883</v>
+        <v>61.51333618164062</v>
       </c>
       <c r="C79" t="n">
         <v>74.30000305175781</v>
@@ -2248,11 +2260,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>61.19046020507812</v>
+        <v>61.19046401977539</v>
       </c>
       <c r="C80" t="n">
         <v>73.91000366210938</v>
@@ -2277,7 +2289,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>57.96773529052734</v>
+        <v>57.96773910522461</v>
       </c>
       <c r="C82" t="n">
         <v>69.59999847412109</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>58.66735458374023</v>
+        <v>58.6673583984375</v>
       </c>
       <c r="C83" t="n">
         <v>70.44000244140625</v>
@@ -2364,11 +2376,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>62.245849609375</v>
+        <v>62.2458610534668</v>
       </c>
       <c r="C84" t="n">
         <v>74.27999877929688</v>
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>63.15087127685547</v>
+        <v>63.15090179443359</v>
       </c>
       <c r="C85" t="n">
         <v>75.36000061035156</v>
@@ -2422,11 +2434,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>61.90230178833008</v>
+        <v>61.90229034423828</v>
       </c>
       <c r="C86" t="n">
         <v>73.87000274658203</v>
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>64.8553466796875</v>
+        <v>64.85531616210938</v>
       </c>
       <c r="C87" t="n">
         <v>76.90000152587891</v>
@@ -2480,7 +2492,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>77.09267425537109</v>
+        <v>77.0926513671875</v>
       </c>
       <c r="C89" t="n">
         <v>91.41000366210938</v>
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>83.94020080566406</v>
+        <v>83.94019317626953</v>
       </c>
       <c r="C90" t="n">
         <v>99.01999664306641</v>
@@ -2567,7 +2579,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2596,7 +2608,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>88.49495697021484</v>
+        <v>88.49494934082031</v>
       </c>
       <c r="C93" t="n">
         <v>103.9199981689453</v>
@@ -2654,7 +2666,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2683,11 +2695,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>111.1296691894531</v>
+        <v>111.1296310424805</v>
       </c>
       <c r="C95" t="n">
         <v>130.5</v>
@@ -2712,11 +2724,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>114.7396240234375</v>
+        <v>114.7396621704102</v>
       </c>
       <c r="C96" t="n">
         <v>134.25</v>
@@ -2741,11 +2753,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>116.6541442871094</v>
+        <v>116.6540985107422</v>
       </c>
       <c r="C97" t="n">
         <v>136.4900054931641</v>
@@ -2770,7 +2782,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2799,11 +2811,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>110.8057174682617</v>
+        <v>110.8056945800781</v>
       </c>
       <c r="C99" t="n">
         <v>128.9199981689453</v>
@@ -2828,7 +2840,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>110.8916549682617</v>
+        <v>110.8916702270508</v>
       </c>
       <c r="C101" t="n">
         <v>129.0200042724609</v>
@@ -2886,11 +2898,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>116.8985443115234</v>
+        <v>116.8985595703125</v>
       </c>
       <c r="C102" t="n">
         <v>135.25</v>
@@ -2915,11 +2927,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>109.9667663574219</v>
+        <v>109.9667510986328</v>
       </c>
       <c r="C103" t="n">
         <v>127.2300033569336</v>
@@ -2944,11 +2956,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>104.1326217651367</v>
+        <v>104.1326141357422</v>
       </c>
       <c r="C104" t="n">
         <v>120.4800033569336</v>
@@ -2973,11 +2985,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>110.2588195800781</v>
+        <v>110.2588043212891</v>
       </c>
       <c r="C105" t="n">
         <v>126.8000030517578</v>
@@ -3002,11 +3014,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>110.7631454467773</v>
+        <v>110.7631378173828</v>
       </c>
       <c r="C106" t="n">
         <v>127.379997253418</v>
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>108.615364074707</v>
+        <v>108.6153945922852</v>
       </c>
       <c r="C107" t="n">
         <v>124.9100036621094</v>
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>117.5143051147461</v>
+        <v>117.5142974853516</v>
       </c>
       <c r="C108" t="n">
         <v>134.3600006103516</v>
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>113.6834487915039</v>
+        <v>113.6834411621094</v>
       </c>
       <c r="C109" t="n">
         <v>129.9799957275391</v>
@@ -3118,11 +3130,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>127.1438827514648</v>
+        <v>127.1439056396484</v>
       </c>
       <c r="C110" t="n">
         <v>145.3699951171875</v>
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>132.7528686523438</v>
+        <v>132.7528533935547</v>
       </c>
       <c r="C111" t="n">
         <v>150.8500061035156</v>
@@ -3176,11 +3188,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>132.0752563476562</v>
+        <v>132.0752105712891</v>
       </c>
       <c r="C112" t="n">
         <v>150.0800018310547</v>
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>126.1438217163086</v>
+        <v>126.1438064575195</v>
       </c>
       <c r="C113" t="n">
         <v>143.3399963378906</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>124.4546127319336</v>
+        <v>124.4546203613281</v>
       </c>
       <c r="C114" t="n">
         <v>140.5200042724609</v>
@@ -3263,11 +3275,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>122.8604049682617</v>
+        <v>122.8604202270508</v>
       </c>
       <c r="C115" t="n">
         <v>138.7200012207031</v>
@@ -3292,7 +3304,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3321,11 +3333,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>116.4780349731445</v>
+        <v>116.4780197143555</v>
       </c>
       <c r="C117" t="n">
         <v>130.6799926757812</v>
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>116.7186813354492</v>
+        <v>116.7186889648438</v>
       </c>
       <c r="C118" t="n">
         <v>130.9499969482422</v>
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>131.9781341552734</v>
+        <v>131.9781188964844</v>
       </c>
       <c r="C119" t="n">
         <v>148.0700073242188</v>
@@ -3408,7 +3420,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3437,7 +3449,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3466,11 +3478,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>107.7365951538086</v>
+        <v>107.7365875244141</v>
       </c>
       <c r="C122" t="n">
         <v>120.129997253418</v>
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>106.9685516357422</v>
+        <v>106.9685592651367</v>
       </c>
       <c r="C123" t="n">
         <v>118.1800003051758</v>
@@ -3524,11 +3536,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>114.8975219726562</v>
+        <v>114.8975524902344</v>
       </c>
       <c r="C124" t="n">
         <v>126.9400024414062</v>
@@ -3553,11 +3565,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>122.0118637084961</v>
+        <v>122.0118865966797</v>
       </c>
       <c r="C125" t="n">
         <v>134.8000030517578</v>
@@ -3582,11 +3594,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>115.1138610839844</v>
+        <v>115.1138458251953</v>
       </c>
       <c r="C126" t="n">
         <v>126.1500015258789</v>
@@ -3611,7 +3623,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3640,11 +3652,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>121.9668579101562</v>
+        <v>121.9668350219727</v>
       </c>
       <c r="C128" t="n">
         <v>133.6600036621094</v>
@@ -3669,11 +3681,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>119.1040496826172</v>
+        <v>119.1040420532227</v>
       </c>
       <c r="C129" t="n">
         <v>129.4499969482422</v>
@@ -3698,11 +3710,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>121.2110366821289</v>
+        <v>121.211051940918</v>
       </c>
       <c r="C130" t="n">
         <v>131.7400054931641</v>
@@ -3727,11 +3739,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>131.046630859375</v>
+        <v>131.0466613769531</v>
       </c>
       <c r="C131" t="n">
         <v>142.4299926757812</v>
@@ -3756,11 +3768,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>139.5906982421875</v>
+        <v>139.5907135009766</v>
       </c>
       <c r="C132" t="n">
         <v>150.5599975585938</v>
@@ -3785,11 +3797,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>144.3376312255859</v>
+        <v>144.337646484375</v>
       </c>
       <c r="C133" t="n">
         <v>155.6799926757812</v>
@@ -3814,11 +3826,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>151.5137481689453</v>
+        <v>151.5137329101562</v>
       </c>
       <c r="C134" t="n">
         <v>163.4199981689453</v>
@@ -3843,11 +3855,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>168.5363922119141</v>
+        <v>168.536376953125</v>
       </c>
       <c r="C135" t="n">
         <v>180.2299957275391</v>
@@ -3872,7 +3884,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3901,11 +3913,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>172.8379364013672</v>
+        <v>172.8379211425781</v>
       </c>
       <c r="C137" t="n">
         <v>184.8300018310547</v>
@@ -3930,11 +3942,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>176.7994384765625</v>
+        <v>176.7994842529297</v>
       </c>
       <c r="C138" t="n">
         <v>187.6300048828125</v>
@@ -3959,11 +3971,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>186.3353118896484</v>
+        <v>186.3353271484375</v>
       </c>
       <c r="C139" t="n">
         <v>197.75</v>
@@ -3988,11 +4000,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>228.4645385742188</v>
+        <v>228.4645080566406</v>
       </c>
       <c r="C140" t="n">
         <v>242.4600067138672</v>
@@ -4017,7 +4029,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4046,11 +4058,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>240.9649353027344</v>
+        <v>240.9649810791016</v>
       </c>
       <c r="C142" t="n">
         <v>254.2100067138672</v>
@@ -4075,11 +4087,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>244.5385131835938</v>
+        <v>244.5385284423828</v>
       </c>
       <c r="C143" t="n">
         <v>257.9800109863281</v>
@@ -4104,11 +4116,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>263.7884521484375</v>
+        <v>263.7884216308594</v>
       </c>
       <c r="C144" t="n">
         <v>276.7999877929688</v>
@@ -4133,11 +4145,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>281.0470886230469</v>
+        <v>281.0471801757812</v>
       </c>
       <c r="C145" t="n">
         <v>294.9100036621094</v>
@@ -4162,7 +4174,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4191,7 +4203,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4220,7 +4232,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4249,7 +4261,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4278,7 +4290,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4307,11 +4319,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>322.9198303222656</v>
+        <v>322.9198608398438</v>
       </c>
       <c r="C151" t="n">
         <v>335.510009765625</v>
@@ -4336,7 +4348,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4365,11 +4377,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>331.5569152832031</v>
+        <v>331.556884765625</v>
       </c>
       <c r="C153" t="n">
         <v>342.7900085449219</v>
@@ -4394,11 +4406,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>359.7129821777344</v>
+        <v>359.7130126953125</v>
       </c>
       <c r="C154" t="n">
         <v>371.8999938964844</v>
@@ -4423,11 +4435,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>343.2313537597656</v>
+        <v>343.2313232421875</v>
       </c>
       <c r="C155" t="n">
         <v>354.8599853515625</v>
@@ -4452,11 +4464,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>336.9456176757812</v>
+        <v>336.9455871582031</v>
       </c>
       <c r="C156" t="n">
         <v>346.760009765625</v>
@@ -4481,11 +4493,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>313.3722534179688</v>
+        <v>313.3722229003906</v>
       </c>
       <c r="C157" t="n">
         <v>322.5</v>
@@ -4510,11 +4522,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>374.7057495117188</v>
+        <v>374.7057189941406</v>
       </c>
       <c r="C158" t="n">
         <v>385.6199951171875</v>
@@ -4539,11 +4551,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>429.6554565429688</v>
+        <v>429.6554260253906</v>
       </c>
       <c r="C159" t="n">
         <v>439.9599914550781</v>
@@ -4568,11 +4580,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>372.4865417480469</v>
+        <v>372.486572265625</v>
       </c>
       <c r="C160" t="n">
         <v>381.4200134277344</v>
@@ -4597,7 +4609,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4626,7 +4638,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4655,7 +4667,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4684,7 +4696,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4713,7 +4725,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4742,7 +4754,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4771,7 +4783,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4800,7 +4812,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4829,7 +4841,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4858,7 +4870,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4885,7 +4897,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4912,7 +4924,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4939,7 +4951,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4966,7 +4978,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4993,7 +5005,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5020,7 +5032,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5047,7 +5059,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5074,7 +5086,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5101,7 +5113,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5128,7 +5140,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5155,7 +5167,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5182,7 +5194,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5209,7 +5221,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5236,7 +5248,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5263,7 +5275,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5290,7 +5302,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5317,7 +5329,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5344,7 +5356,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5371,7 +5383,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5398,7 +5410,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5425,7 +5437,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5452,7 +5464,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5479,7 +5491,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5506,7 +5518,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5533,7 +5545,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5560,7 +5572,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5587,7 +5599,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5614,7 +5626,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5641,7 +5653,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5668,7 +5680,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5695,7 +5707,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5722,7 +5734,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5749,7 +5761,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5776,7 +5788,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5803,7 +5815,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5830,7 +5842,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5857,7 +5869,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5884,7 +5896,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5911,7 +5923,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5938,7 +5950,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5965,7 +5977,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -5992,7 +6004,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6019,7 +6031,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6046,7 +6058,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6073,7 +6085,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6100,7 +6112,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6127,7 +6139,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6154,7 +6166,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6181,7 +6193,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6208,7 +6220,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6235,7 +6247,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6262,7 +6274,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6289,7 +6301,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6316,7 +6328,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6343,7 +6355,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6370,7 +6382,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6397,7 +6409,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6424,7 +6436,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6451,7 +6463,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6478,7 +6490,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6505,7 +6517,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6532,7 +6544,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6559,7 +6571,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6586,7 +6598,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6613,7 +6625,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6640,7 +6652,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6667,7 +6679,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6694,7 +6706,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6721,7 +6733,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6748,7 +6760,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6775,7 +6787,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6802,7 +6814,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6831,7 +6843,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6860,7 +6872,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6889,7 +6901,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6918,7 +6930,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6947,7 +6959,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6976,7 +6988,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7005,7 +7017,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7034,32 +7046,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>199.9299926757812</v>
+        <v>196.8000030517578</v>
       </c>
       <c r="C250" t="n">
-        <v>199.9299926757812</v>
+        <v>196.8000030517578</v>
       </c>
       <c r="D250" t="n">
-        <v>105449900</v>
+        <v>115083700</v>
       </c>
       <c r="E250" t="n">
         <v>2.779999999999998</v>
       </c>
       <c r="F250" t="n">
-        <v>71.91726355243934</v>
+        <v>70.79136800422947</v>
       </c>
       <c r="G250" t="n">
         <v>790370020</v>
       </c>
       <c r="H250" t="n">
-        <v>158018672309.7571</v>
+        <v>155544822348.0179</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1334183956015943</v>
+        <v>0.1456073700771191</v>
       </c>
     </row>
   </sheetData>
@@ -7091,75 +7103,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40016</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7195,13 +7207,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40107</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7237,13 +7249,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40289</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7279,13 +7291,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40016</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7321,13 +7333,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40107</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7363,13 +7375,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7396,7 +7408,7 @@
       <c r="I7" t="n">
         <v>1.79</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="K7" t="n">
@@ -7409,13 +7421,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40289</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7442,7 +7454,7 @@
       <c r="I8" t="n">
         <v>1.63</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="K8" t="n">
@@ -7455,13 +7467,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40387</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7488,7 +7500,7 @@
       <c r="I9" t="n">
         <v>1.28</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="K9" t="n">
@@ -7501,13 +7513,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40471</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7534,7 +7546,7 @@
       <c r="I10" t="n">
         <v>4.63</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="K10" t="n">
@@ -7547,13 +7559,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7580,7 +7592,7 @@
       <c r="I11" t="n">
         <v>4.44</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="K11" t="n">
@@ -7593,13 +7605,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7626,7 +7638,7 @@
       <c r="I12" t="n">
         <v>4.52</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="K12" t="n">
@@ -7639,13 +7651,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7672,7 +7684,7 @@
       <c r="I13" t="n">
         <v>4.710000000000001</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="K13" t="n">
@@ -7685,13 +7697,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7718,7 +7730,7 @@
       <c r="I14" t="n">
         <v>5.050000000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="K14" t="n">
@@ -7731,13 +7743,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40948</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7764,7 +7776,7 @@
       <c r="I15" t="n">
         <v>5.33</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40948</v>
       </c>
       <c r="K15" t="n">
@@ -7777,13 +7789,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7810,7 +7822,7 @@
       <c r="I16" t="n">
         <v>5.77</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="K16" t="n">
@@ -7823,13 +7835,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7856,7 +7868,7 @@
       <c r="I17" t="n">
         <v>5.79</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="K17" t="n">
@@ -7869,13 +7881,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7902,7 +7914,7 @@
       <c r="I18" t="n">
         <v>5.68</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="K18" t="n">
@@ -7915,13 +7927,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41316</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7948,7 +7960,7 @@
       <c r="I19" t="n">
         <v>5.12</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41316</v>
       </c>
       <c r="K19" t="n">
@@ -7961,13 +7973,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7994,7 +8006,7 @@
       <c r="I20" t="n">
         <v>5.34</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="K20" t="n">
@@ -8007,13 +8019,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8040,7 +8052,7 @@
       <c r="I21" t="n">
         <v>5.48</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="K21" t="n">
@@ -8053,13 +8065,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8086,7 +8098,7 @@
       <c r="I22" t="n">
         <v>5.640000000000001</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="K22" t="n">
@@ -8099,13 +8111,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8132,7 +8144,7 @@
       <c r="I23" t="n">
         <v>5.97</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="K23" t="n">
@@ -8145,13 +8157,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8178,7 +8190,7 @@
       <c r="I24" t="n">
         <v>5.81</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="K24" t="n">
@@ -8191,13 +8203,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8224,7 +8236,7 @@
       <c r="I25" t="n">
         <v>6.640000000000001</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="K25" t="n">
@@ -8237,13 +8249,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41934</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8270,7 +8282,7 @@
       <c r="I26" t="n">
         <v>6.990000000000001</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41934</v>
       </c>
       <c r="K26" t="n">
@@ -8283,13 +8295,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8316,7 +8328,7 @@
       <c r="I27" t="n">
         <v>7.4</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="K27" t="n">
@@ -8329,13 +8341,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42116</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8362,7 +8374,7 @@
       <c r="I28" t="n">
         <v>7.99</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42116</v>
       </c>
       <c r="K28" t="n">
@@ -8375,13 +8387,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42207</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8408,7 +8420,7 @@
       <c r="I29" t="n">
         <v>7.34</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42207</v>
       </c>
       <c r="K29" t="n">
@@ -8421,13 +8433,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42298</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8454,7 +8466,7 @@
       <c r="I30" t="n">
         <v>7.95</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42298</v>
       </c>
       <c r="K30" t="n">
@@ -8467,13 +8479,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8500,7 +8512,7 @@
       <c r="I31" t="n">
         <v>7.44</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="K31" t="n">
@@ -8513,13 +8525,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8546,7 +8558,7 @@
       <c r="I32" t="n">
         <v>7.4</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="K32" t="n">
@@ -8559,13 +8571,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8592,7 +8604,7 @@
       <c r="I33" t="n">
         <v>5.44</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="K33" t="n">
@@ -8605,13 +8617,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8638,7 +8650,7 @@
       <c r="I34" t="n">
         <v>6.57</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="K34" t="n">
@@ -8651,13 +8663,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42774</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8684,7 +8696,7 @@
       <c r="I35" t="n">
         <v>7.65</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42774</v>
       </c>
       <c r="K35" t="n">
@@ -8697,13 +8709,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8730,7 +8742,7 @@
       <c r="I36" t="n">
         <v>8.16</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="K36" t="n">
@@ -8743,13 +8755,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8776,7 +8788,7 @@
       <c r="I37" t="n">
         <v>11.42</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="K37" t="n">
@@ -8789,13 +8801,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43033</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8822,7 +8834,7 @@
       <c r="I38" t="n">
         <v>10.88</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43033</v>
       </c>
       <c r="K38" t="n">
@@ -8835,13 +8847,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43143</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8868,7 +8880,7 @@
       <c r="I39" t="n">
         <v>13.47</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43143</v>
       </c>
       <c r="K39" t="n">
@@ -8881,13 +8893,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8914,7 +8926,7 @@
       <c r="I40" t="n">
         <v>15.28</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="K40" t="n">
@@ -8927,13 +8939,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8960,7 +8972,7 @@
       <c r="I41" t="n">
         <v>16.12</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="K41" t="n">
@@ -8973,13 +8985,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9006,7 +9018,7 @@
       <c r="I42" t="n">
         <v>17.13</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="K42" t="n">
@@ -9019,13 +9031,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9052,7 +9064,7 @@
       <c r="I43" t="n">
         <v>17.88</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="K43" t="n">
@@ -9065,13 +9077,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9098,7 +9110,7 @@
       <c r="I44" t="n">
         <v>17.48</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="K44" t="n">
@@ -9111,13 +9123,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43670</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9144,7 +9156,7 @@
       <c r="I45" t="n">
         <v>8.539999999999999</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43670</v>
       </c>
       <c r="K45" t="n">
@@ -9157,13 +9169,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43761</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9190,7 +9202,7 @@
       <c r="I46" t="n">
         <v>6.52</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43761</v>
       </c>
       <c r="K46" t="n">
@@ -9203,13 +9215,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9236,7 +9248,7 @@
       <c r="I47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="K47" t="n">
@@ -9249,13 +9261,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9282,7 +9294,7 @@
       <c r="I48" t="n">
         <v>-6.06</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="K48" t="n">
@@ -9295,13 +9307,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9328,7 +9340,7 @@
       <c r="I49" t="n">
         <v>-5.050000000000001</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="K49" t="n">
@@ -9341,13 +9353,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9374,7 +9386,7 @@
       <c r="I50" t="n">
         <v>-7.890000000000001</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="K50" t="n">
@@ -9387,13 +9399,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9420,7 +9432,7 @@
       <c r="I51" t="n">
         <v>-20.75</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="K51" t="n">
@@ -9433,13 +9445,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9466,7 +9478,7 @@
       <c r="I52" t="n">
         <v>-20.56</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="K52" t="n">
@@ -9479,13 +9491,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9512,7 +9524,7 @@
       <c r="I53" t="n">
         <v>-15.36</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="K53" t="n">
@@ -9525,13 +9537,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9558,7 +9570,7 @@
       <c r="I54" t="n">
         <v>-14.76</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="K54" t="n">
@@ -9571,13 +9583,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9604,7 +9616,7 @@
       <c r="I55" t="n">
         <v>-7.150000000000002</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="K55" t="n">
@@ -9617,13 +9629,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9650,7 +9662,7 @@
       <c r="I56" t="n">
         <v>-8.290000000000003</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="K56" t="n">
@@ -9663,13 +9675,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9696,7 +9708,7 @@
       <c r="I57" t="n">
         <v>-8.970000000000002</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="K57" t="n">
@@ -9709,13 +9721,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9742,7 +9754,7 @@
       <c r="I58" t="n">
         <v>-14.27</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="K58" t="n">
@@ -9755,13 +9767,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9788,7 +9800,7 @@
       <c r="I59" t="n">
         <v>-8.300000000000002</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="K59" t="n">
@@ -9801,13 +9813,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9834,7 +9846,7 @@
       <c r="I60" t="n">
         <v>-6.930000000000001</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="K60" t="n">
@@ -9847,13 +9859,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9880,7 +9892,7 @@
       <c r="I61" t="n">
         <v>-7.500000000000002</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="K61" t="n">
@@ -9893,13 +9905,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9926,7 +9938,7 @@
       <c r="I62" t="n">
         <v>-4.710000000000003</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="K62" t="n">
@@ -9939,13 +9951,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9972,7 +9984,7 @@
       <c r="I63" t="n">
         <v>-3.670000000000002</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="K63" t="n">
@@ -9985,13 +9997,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10018,7 +10030,7 @@
       <c r="I64" t="n">
         <v>-3.540000000000002</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="K64" t="n">
@@ -10031,13 +10043,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10064,7 +10076,7 @@
       <c r="I65" t="n">
         <v>-5.620000000000002</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="K65" t="n">
@@ -10077,13 +10089,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10110,7 +10122,7 @@
       <c r="I66" t="n">
         <v>-12.89</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="K66" t="n">
@@ -10123,13 +10135,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45691</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10156,7 +10168,7 @@
       <c r="I67" t="n">
         <v>-18.36</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45691</v>
       </c>
       <c r="K67" t="n">
@@ -10169,13 +10181,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10202,7 +10214,7 @@
       <c r="I68" t="n">
         <v>-17.96</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="K68" t="n">
@@ -10215,13 +10227,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10248,7 +10260,7 @@
       <c r="I69" t="n">
         <v>-16.55</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="K69" t="n">
@@ -10261,13 +10273,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10294,7 +10306,7 @@
       <c r="I70" t="n">
         <v>-13.72</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="K70" t="n">
@@ -10307,13 +10319,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10340,7 +10352,7 @@
       <c r="I71" t="n">
         <v>2.479999999999999</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="K71" t="n">
@@ -10353,13 +10365,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10386,7 +10398,7 @@
       <c r="I72" t="n">
         <v>2.529999999999999</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="K72" t="n">
@@ -10399,13 +10411,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46231</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10432,7 +10444,7 @@
       <c r="I73" t="n">
         <v>2.779999999999998</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46231</v>
       </c>
       <c r="K73" t="n">
@@ -10469,52 +10481,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40016</v>
       </c>
       <c r="C2" t="n">
@@ -10543,10 +10555,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40102</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40107</v>
       </c>
       <c r="C3" t="n">
@@ -10575,10 +10587,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40210</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40217</v>
       </c>
       <c r="C4" t="n">
@@ -10607,10 +10619,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40284</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40289</v>
       </c>
       <c r="C5" t="n">
@@ -10639,10 +10651,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40380</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40387</v>
       </c>
       <c r="C6" t="n">
@@ -10671,10 +10683,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40464</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40471</v>
       </c>
       <c r="C7" t="n">
@@ -10703,10 +10715,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40575</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="C8" t="n">
@@ -10735,10 +10747,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40653</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="C9" t="n">
@@ -10767,10 +10779,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40744</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="C10" t="n">
@@ -10799,10 +10811,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40835</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="C11" t="n">
@@ -10831,10 +10843,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40940</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40948</v>
       </c>
       <c r="C12" t="n">
@@ -10863,10 +10875,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41017</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="C13" t="n">
@@ -10895,10 +10907,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41108</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="C14" t="n">
@@ -10927,10 +10939,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41199</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="C15" t="n">
@@ -10959,10 +10971,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41316</v>
       </c>
       <c r="C16" t="n">
@@ -10991,10 +11003,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41381</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="C17" t="n">
@@ -11023,10 +11035,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41472</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="C18" t="n">
@@ -11055,10 +11067,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41563</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="C19" t="n">
@@ -11087,10 +11099,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41677</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41684</v>
       </c>
       <c r="C20" t="n">
@@ -11119,10 +11131,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41745</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="C21" t="n">
@@ -11151,10 +11163,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41836</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="C22" t="n">
@@ -11183,10 +11195,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41927</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41934</v>
       </c>
       <c r="C23" t="n">
@@ -11215,10 +11227,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42040</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="C24" t="n">
@@ -11247,10 +11259,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42109</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42116</v>
       </c>
       <c r="C25" t="n">
@@ -11279,10 +11291,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42200</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42207</v>
       </c>
       <c r="C26" t="n">
@@ -11311,10 +11323,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42291</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42298</v>
       </c>
       <c r="C27" t="n">
@@ -11343,10 +11355,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42404</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="C28" t="n">
@@ -11375,10 +11387,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42480</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="C29" t="n">
@@ -11407,10 +11419,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42571</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="C30" t="n">
@@ -11439,10 +11451,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42662</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="C31" t="n">
@@ -11471,10 +11483,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42767</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42774</v>
       </c>
       <c r="C32" t="n">
@@ -11503,10 +11515,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42844</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="C33" t="n">
@@ -11535,10 +11547,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42935</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="C34" t="n">
@@ -11567,10 +11579,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43026</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43033</v>
       </c>
       <c r="C35" t="n">
@@ -11599,10 +11611,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43136</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43143</v>
       </c>
       <c r="C36" t="n">
@@ -11631,10 +11643,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43208</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="C37" t="n">
@@ -11663,10 +11675,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43299</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="C38" t="n">
@@ -11695,10 +11707,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43390</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="C39" t="n">
@@ -11727,10 +11739,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43497</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="C40" t="n">
@@ -11759,10 +11771,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43572</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="C41" t="n">
@@ -11791,10 +11803,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43663</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43670</v>
       </c>
       <c r="C42" t="n">
@@ -11823,10 +11835,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43754</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43761</v>
       </c>
       <c r="C43" t="n">
@@ -11855,10 +11867,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43854</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="C44" t="n">
@@ -11887,10 +11899,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43943</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="C45" t="n">
@@ -11919,10 +11931,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44034</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="C46" t="n">
@@ -11951,10 +11963,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44125</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="C47" t="n">
@@ -11983,10 +11995,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44221</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="C48" t="n">
@@ -12015,10 +12027,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44307</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="C49" t="n">
@@ -12047,10 +12059,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44398</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="C50" t="n">
@@ -12079,10 +12091,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44489</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="C51" t="n">
@@ -12111,10 +12123,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44585</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="C52" t="n">
@@ -12143,10 +12155,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44671</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="C53" t="n">
@@ -12175,10 +12187,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44762</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="C54" t="n">
@@ -12207,10 +12219,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44853</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="C55" t="n">
@@ -12239,10 +12251,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44946</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="C56" t="n">
@@ -12271,10 +12283,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45035</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="C57" t="n">
@@ -12303,10 +12315,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45126</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="C58" t="n">
@@ -12335,10 +12347,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45217</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="C59" t="n">
@@ -12367,10 +12379,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45315</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="C60" t="n">
@@ -12399,10 +12411,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45399</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="C61" t="n">
@@ -12431,10 +12443,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45497</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="C62" t="n">
@@ -12463,10 +12475,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45581</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="C63" t="n">
@@ -12495,10 +12507,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45684</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45691</v>
       </c>
       <c r="C64" t="n">
@@ -12527,10 +12539,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45763</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="C65" t="n">
@@ -12559,10 +12571,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45860</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45867</v>
       </c>
       <c r="C66" t="n">
@@ -12591,10 +12603,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45952</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="C67" t="n">
@@ -12623,10 +12635,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46045</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="C68" t="n">
@@ -12655,10 +12667,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46127</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="C69" t="n">
@@ -12687,10 +12699,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46224</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46231</v>
       </c>
       <c r="C70" t="n">
@@ -12737,12 +12749,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/BA.xlsx
+++ b/salidas/empresas/BA.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>48.60415267944336</v>
+        <v>48.60414505004883</v>
       </c>
       <c r="C2" t="n">
         <v>68.30999755859375</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>51.93840026855469</v>
+        <v>51.93839645385742</v>
       </c>
       <c r="C3" t="n">
         <v>72.69000244140625</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>55.68249130249023</v>
+        <v>55.68246459960938</v>
       </c>
       <c r="C4" t="n">
         <v>77.93000030517578</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>59.62662887573242</v>
+        <v>59.62661361694336</v>
       </c>
       <c r="C5" t="n">
         <v>83.44999694824219</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>59.68720626831055</v>
+        <v>59.68721389770508</v>
       </c>
       <c r="C6" t="n">
         <v>83.25</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>58.72649765014648</v>
+        <v>58.72648620605469</v>
       </c>
       <c r="C7" t="n">
         <v>81.91000366210938</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>55.50732803344727</v>
+        <v>55.50731658935547</v>
       </c>
       <c r="C8" t="n">
         <v>77.41999816894531</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>53.90749740600586</v>
+        <v>53.90752410888672</v>
       </c>
       <c r="C9" t="n">
         <v>74.90000152587891</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>56.75042724609375</v>
+        <v>56.75043869018555</v>
       </c>
       <c r="C10" t="n">
         <v>78.84999847412109</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>57.47734069824219</v>
+        <v>57.47737503051758</v>
       </c>
       <c r="C11" t="n">
         <v>79.86000061035156</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>63.94344711303711</v>
+        <v>63.94345092773438</v>
       </c>
       <c r="C12" t="n">
         <v>88.52999877929688</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>64.16736602783203</v>
+        <v>64.16738128662109</v>
       </c>
       <c r="C13" t="n">
         <v>88.83999633789062</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>64.68744659423828</v>
+        <v>64.68741607666016</v>
       </c>
       <c r="C14" t="n">
         <v>89.55999755859375</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>63.2695426940918</v>
+        <v>63.26957321166992</v>
       </c>
       <c r="C15" t="n">
         <v>87.26000213623047</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>64.46592712402344</v>
+        <v>64.46593475341797</v>
       </c>
       <c r="C16" t="n">
         <v>88.91000366210938</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>73.20668792724609</v>
+        <v>73.20672607421875</v>
       </c>
       <c r="C18" t="n">
         <v>100.5899963378906</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>69.98267364501953</v>
+        <v>69.98268127441406</v>
       </c>
       <c r="C19" t="n">
         <v>96.16000366210938</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>75.27359771728516</v>
+        <v>75.27359008789062</v>
       </c>
       <c r="C20" t="n">
         <v>103.4300003051758</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>70.6151123046875</v>
+        <v>70.61509704589844</v>
       </c>
       <c r="C21" t="n">
         <v>96.69999694824219</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>76.66888427734375</v>
+        <v>76.66887664794922</v>
       </c>
       <c r="C22" t="n">
         <v>104.9899978637695</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>71.99526214599609</v>
+        <v>71.99529266357422</v>
       </c>
       <c r="C23" t="n">
         <v>98.58999633789062</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>67.82022857666016</v>
+        <v>67.82021331787109</v>
       </c>
       <c r="C24" t="n">
         <v>92.54000091552734</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>60.96051788330078</v>
+        <v>60.96052932739258</v>
       </c>
       <c r="C26" t="n">
         <v>83.18000030517578</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>60.97327423095703</v>
+        <v>60.9732666015625</v>
       </c>
       <c r="C27" t="n">
         <v>82.79000091552734</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>54.77210235595703</v>
+        <v>54.77211380004883</v>
       </c>
       <c r="C28" t="n">
         <v>74.37000274658203</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>62.49778747558594</v>
+        <v>62.49776840209961</v>
       </c>
       <c r="C29" t="n">
         <v>84.86000061035156</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>61.24287796020508</v>
+        <v>61.242919921875</v>
       </c>
       <c r="C30" t="n">
         <v>82.76999664306641</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>45.21631622314453</v>
+        <v>45.21630096435547</v>
       </c>
       <c r="C32" t="n">
         <v>61.11000061035156</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>48.80837249755859</v>
+        <v>48.80836868286133</v>
       </c>
       <c r="C33" t="n">
         <v>65.55999755859375</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>42.69614791870117</v>
+        <v>42.69616317749023</v>
       </c>
       <c r="C34" t="n">
         <v>57.34999847412109</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>39.02584457397461</v>
+        <v>39.02584838867188</v>
       </c>
       <c r="C35" t="n">
         <v>52.41999816894531</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>31.97589302062988</v>
+        <v>31.97589683532715</v>
       </c>
       <c r="C36" t="n">
         <v>42.63000106811523</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>31.73586845397949</v>
+        <v>31.73585319519043</v>
       </c>
       <c r="C38" t="n">
         <v>42.31000137329102</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>23.82019424438477</v>
+        <v>23.8201904296875</v>
       </c>
       <c r="C39" t="n">
         <v>31.44000053405762</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>26.95681762695312</v>
+        <v>26.95681953430176</v>
       </c>
       <c r="C40" t="n">
         <v>35.58000183105469</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>32.51619338989258</v>
+        <v>32.51618576049805</v>
       </c>
       <c r="C43" t="n">
         <v>42.5</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>32.82987594604492</v>
+        <v>32.82986450195312</v>
       </c>
       <c r="C44" t="n">
         <v>42.90999984741211</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>41.82724761962891</v>
+        <v>41.82725524902344</v>
       </c>
       <c r="C46" t="n">
         <v>54.15000152587891</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>36.92229461669922</v>
+        <v>36.92230606079102</v>
       </c>
       <c r="C47" t="n">
         <v>47.79999923706055</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>42.18012237548828</v>
+        <v>42.18010330200195</v>
       </c>
       <c r="C49" t="n">
         <v>54.13000106811523</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>47.22177505493164</v>
+        <v>47.22178268432617</v>
       </c>
       <c r="C50" t="n">
         <v>60.59999847412109</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>56.96667861938477</v>
+        <v>56.9666748046875</v>
       </c>
       <c r="C52" t="n">
         <v>72.61000061035156</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>56.82547378540039</v>
+        <v>56.82548141479492</v>
       </c>
       <c r="C53" t="n">
         <v>72.43000030517578</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>50.64509963989258</v>
+        <v>50.64510345458984</v>
       </c>
       <c r="C54" t="n">
         <v>64.18000030517578</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>49.51667404174805</v>
+        <v>49.51666641235352</v>
       </c>
       <c r="C55" t="n">
         <v>62.75</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>53.76998519897461</v>
+        <v>53.76996994018555</v>
       </c>
       <c r="C56" t="n">
         <v>68.13999938964844</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>48.53142547607422</v>
+        <v>48.53144454956055</v>
       </c>
       <c r="C57" t="n">
         <v>61.13000106811523</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>52.82645034790039</v>
+        <v>52.82646942138672</v>
       </c>
       <c r="C58" t="n">
         <v>66.54000091552734</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>56.08146286010742</v>
+        <v>56.08148574829102</v>
       </c>
       <c r="C59" t="n">
         <v>70.63999938964844</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>50.93391418457031</v>
+        <v>50.93390274047852</v>
       </c>
       <c r="C60" t="n">
         <v>63.77000045776367</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>55.49456405639648</v>
+        <v>55.49456787109375</v>
       </c>
       <c r="C62" t="n">
         <v>69.48000335693359</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>57.84945297241211</v>
+        <v>57.84946060180664</v>
       </c>
       <c r="C63" t="n">
         <v>72.01000213623047</v>
@@ -1800,7 +1800,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>59.39189910888672</v>
+        <v>59.39188003540039</v>
       </c>
       <c r="C64" t="n">
         <v>73.93000030517578</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>63.01667404174805</v>
+        <v>63.01666641235352</v>
       </c>
       <c r="C66" t="n">
         <v>78.02999877929688</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>59.70553588867188</v>
+        <v>59.70553207397461</v>
       </c>
       <c r="C67" t="n">
         <v>73.93000030517578</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>56.91125869750977</v>
+        <v>56.91125106811523</v>
       </c>
       <c r="C68" t="n">
         <v>70.47000122070312</v>
@@ -1945,7 +1945,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>54.36209106445312</v>
+        <v>54.36209487915039</v>
       </c>
       <c r="C69" t="n">
         <v>66.86000061035156</v>
@@ -1974,7 +1974,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>49.19906997680664</v>
+        <v>49.19907379150391</v>
       </c>
       <c r="C70" t="n">
         <v>60.5099983215332</v>
@@ -2003,7 +2003,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>53.49211120605469</v>
+        <v>53.49209213256836</v>
       </c>
       <c r="C71" t="n">
         <v>65.79000091552734</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>56.20613098144531</v>
+        <v>56.20611190795898</v>
       </c>
       <c r="C72" t="n">
         <v>68.69000244140625</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>60.01921081542969</v>
+        <v>60.01921844482422</v>
       </c>
       <c r="C73" t="n">
         <v>73.34999847412109</v>
@@ -2090,7 +2090,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>60.6983757019043</v>
+        <v>60.69836044311523</v>
       </c>
       <c r="C74" t="n">
         <v>74.18000030517578</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>61.68936920166016</v>
+        <v>61.68938446044922</v>
       </c>
       <c r="C75" t="n">
         <v>74.94999694824219</v>
@@ -2148,7 +2148,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>61.21197509765625</v>
+        <v>61.21199798583984</v>
       </c>
       <c r="C76" t="n">
         <v>74.37000274658203</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>63.21207427978516</v>
+        <v>63.21205902099609</v>
       </c>
       <c r="C77" t="n">
         <v>76.80000305175781</v>
@@ -2206,7 +2206,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>57.63045501708984</v>
+        <v>57.63047409057617</v>
       </c>
       <c r="C78" t="n">
         <v>69.61000061035156</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>61.51333618164062</v>
+        <v>61.5133171081543</v>
       </c>
       <c r="C79" t="n">
         <v>74.30000305175781</v>
@@ -2264,7 +2264,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>61.19046401977539</v>
+        <v>61.19046020507812</v>
       </c>
       <c r="C80" t="n">
         <v>73.91000366210938</v>
@@ -2293,7 +2293,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>59.46689987182617</v>
+        <v>59.4669189453125</v>
       </c>
       <c r="C81" t="n">
         <v>71.40000152587891</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>57.96773910522461</v>
+        <v>57.96772766113281</v>
       </c>
       <c r="C82" t="n">
         <v>69.59999847412109</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>62.2458610534668</v>
+        <v>62.24584197998047</v>
       </c>
       <c r="C84" t="n">
         <v>74.27999877929688</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>63.15090179443359</v>
+        <v>63.15088653564453</v>
       </c>
       <c r="C85" t="n">
         <v>75.36000061035156</v>
@@ -2467,7 +2467,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>64.85531616210938</v>
+        <v>64.85532379150391</v>
       </c>
       <c r="C87" t="n">
         <v>76.90000152587891</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>72.40350341796875</v>
+        <v>72.40351104736328</v>
       </c>
       <c r="C88" t="n">
         <v>85.84999847412109</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>83.94019317626953</v>
+        <v>83.94020080566406</v>
       </c>
       <c r="C90" t="n">
         <v>99.01999664306641</v>
@@ -2583,7 +2583,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>86.83937072753906</v>
+        <v>86.83936309814453</v>
       </c>
       <c r="C91" t="n">
         <v>102.4400024414062</v>
@@ -2641,7 +2641,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>88.49494934082031</v>
+        <v>88.49495697021484</v>
       </c>
       <c r="C93" t="n">
         <v>103.9199981689453</v>
@@ -2699,7 +2699,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>111.1296310424805</v>
+        <v>111.129638671875</v>
       </c>
       <c r="C95" t="n">
         <v>130.5</v>
@@ -2728,7 +2728,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>114.7396621704102</v>
+        <v>114.7396469116211</v>
       </c>
       <c r="C96" t="n">
         <v>134.25</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>116.6540985107422</v>
+        <v>116.6540908813477</v>
       </c>
       <c r="C97" t="n">
         <v>136.4900054931641</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>107.0561447143555</v>
+        <v>107.0561599731445</v>
       </c>
       <c r="C98" t="n">
         <v>125.2600021362305</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>110.8056945800781</v>
+        <v>110.8056869506836</v>
       </c>
       <c r="C99" t="n">
         <v>128.9199981689453</v>
@@ -2873,7 +2873,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>110.8916702270508</v>
+        <v>110.8916473388672</v>
       </c>
       <c r="C101" t="n">
         <v>129.0200042724609</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>116.8985595703125</v>
+        <v>116.8985366821289</v>
       </c>
       <c r="C102" t="n">
         <v>135.25</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>104.1326141357422</v>
+        <v>104.1326217651367</v>
       </c>
       <c r="C104" t="n">
         <v>120.4800033569336</v>
@@ -2989,7 +2989,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>110.2588043212891</v>
+        <v>110.2587966918945</v>
       </c>
       <c r="C105" t="n">
         <v>126.8000030517578</v>
@@ -3018,7 +3018,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>110.7631378173828</v>
+        <v>110.7631530761719</v>
       </c>
       <c r="C106" t="n">
         <v>127.379997253418</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>108.6153945922852</v>
+        <v>108.615364074707</v>
       </c>
       <c r="C107" t="n">
         <v>124.9100036621094</v>
@@ -3076,7 +3076,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>117.5142974853516</v>
+        <v>117.5143051147461</v>
       </c>
       <c r="C108" t="n">
         <v>134.3600006103516</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>113.6834411621094</v>
+        <v>113.683464050293</v>
       </c>
       <c r="C109" t="n">
         <v>129.9799957275391</v>
@@ -3192,7 +3192,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>132.0752105712891</v>
+        <v>132.0752258300781</v>
       </c>
       <c r="C112" t="n">
         <v>150.0800018310547</v>
@@ -3221,7 +3221,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>126.1438064575195</v>
+        <v>126.143798828125</v>
       </c>
       <c r="C113" t="n">
         <v>143.3399963378906</v>
@@ -3250,7 +3250,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>124.4546203613281</v>
+        <v>124.4546127319336</v>
       </c>
       <c r="C114" t="n">
         <v>140.5200042724609</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>122.8604202270508</v>
+        <v>122.8604049682617</v>
       </c>
       <c r="C115" t="n">
         <v>138.7200012207031</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>127.6873168945312</v>
+        <v>127.6873092651367</v>
       </c>
       <c r="C116" t="n">
         <v>144.1699981689453</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>116.4780197143555</v>
+        <v>116.4780120849609</v>
       </c>
       <c r="C117" t="n">
         <v>130.6799926757812</v>
@@ -3366,7 +3366,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>116.7186889648438</v>
+        <v>116.7186965942383</v>
       </c>
       <c r="C118" t="n">
         <v>130.9499969482422</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>131.9781188964844</v>
+        <v>131.9781646728516</v>
       </c>
       <c r="C119" t="n">
         <v>148.0700073242188</v>
@@ -3424,7 +3424,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>130.4444427490234</v>
+        <v>130.4444274902344</v>
       </c>
       <c r="C120" t="n">
         <v>145.4499969482422</v>
@@ -3482,7 +3482,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>107.7365875244141</v>
+        <v>107.7366104125977</v>
       </c>
       <c r="C122" t="n">
         <v>120.129997253418</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>114.8975524902344</v>
+        <v>114.8975448608398</v>
       </c>
       <c r="C124" t="n">
         <v>126.9400024414062</v>
@@ -3598,7 +3598,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>115.1138458251953</v>
+        <v>115.1138534545898</v>
       </c>
       <c r="C126" t="n">
         <v>126.1500015258789</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>118.5083999633789</v>
+        <v>118.5083770751953</v>
       </c>
       <c r="C127" t="n">
         <v>129.8699951171875</v>
@@ -3685,7 +3685,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>119.1040420532227</v>
+        <v>119.1040649414062</v>
       </c>
       <c r="C129" t="n">
         <v>129.4499969482422</v>
@@ -3743,7 +3743,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>131.0466613769531</v>
+        <v>131.0466766357422</v>
       </c>
       <c r="C131" t="n">
         <v>142.4299926757812</v>
@@ -3772,7 +3772,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>139.5907135009766</v>
+        <v>139.5906829833984</v>
       </c>
       <c r="C132" t="n">
         <v>150.5599975585938</v>
@@ -3830,7 +3830,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>151.5137329101562</v>
+        <v>151.5137481689453</v>
       </c>
       <c r="C134" t="n">
         <v>163.4199981689453</v>
@@ -3859,7 +3859,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>168.536376953125</v>
+        <v>168.5364074707031</v>
       </c>
       <c r="C135" t="n">
         <v>180.2299957275391</v>
@@ -3917,7 +3917,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>172.8379211425781</v>
+        <v>172.8379516601562</v>
       </c>
       <c r="C137" t="n">
         <v>184.8300018310547</v>
@@ -3946,7 +3946,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>176.7994842529297</v>
+        <v>176.7994689941406</v>
       </c>
       <c r="C138" t="n">
         <v>187.6300048828125</v>
@@ -4004,7 +4004,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>228.4645080566406</v>
+        <v>228.4645233154297</v>
       </c>
       <c r="C140" t="n">
         <v>242.4600067138672</v>
@@ -4033,7 +4033,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>227.1730651855469</v>
+        <v>227.1730194091797</v>
       </c>
       <c r="C141" t="n">
         <v>239.6600036621094</v>
@@ -4062,7 +4062,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>240.9649810791016</v>
+        <v>240.9649505615234</v>
       </c>
       <c r="C142" t="n">
         <v>254.2100067138672</v>
@@ -4091,7 +4091,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>244.5385284423828</v>
+        <v>244.5385131835938</v>
       </c>
       <c r="C143" t="n">
         <v>257.9800109863281</v>
@@ -4149,7 +4149,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>281.0471801757812</v>
+        <v>281.047119140625</v>
       </c>
       <c r="C145" t="n">
         <v>294.9100036621094</v>
@@ -4178,7 +4178,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>337.7120666503906</v>
+        <v>337.7120971679688</v>
       </c>
       <c r="C146" t="n">
         <v>354.3699951171875</v>
@@ -4207,7 +4207,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>346.8874816894531</v>
+        <v>346.887451171875</v>
       </c>
       <c r="C147" t="n">
         <v>362.2099914550781</v>
@@ -4236,7 +4236,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>314.009765625</v>
+        <v>314.0097351074219</v>
       </c>
       <c r="C148" t="n">
         <v>327.8800048828125</v>
@@ -4294,7 +4294,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>338.945068359375</v>
+        <v>338.9450378417969</v>
       </c>
       <c r="C150" t="n">
         <v>352.1600036621094</v>
@@ -4381,7 +4381,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>331.556884765625</v>
+        <v>331.5569152832031</v>
       </c>
       <c r="C153" t="n">
         <v>342.7900085449219</v>
@@ -4410,7 +4410,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>359.7130126953125</v>
+        <v>359.7129821777344</v>
       </c>
       <c r="C154" t="n">
         <v>371.8999938964844</v>
@@ -4439,7 +4439,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>343.2313232421875</v>
+        <v>343.2313537597656</v>
       </c>
       <c r="C155" t="n">
         <v>354.8599853515625</v>
@@ -4497,7 +4497,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>313.3722229003906</v>
+        <v>313.3721923828125</v>
       </c>
       <c r="C157" t="n">
         <v>322.5</v>
@@ -4526,7 +4526,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>374.7057189941406</v>
+        <v>374.7057495117188</v>
       </c>
       <c r="C158" t="n">
         <v>385.6199951171875</v>
@@ -4555,7 +4555,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>429.6554260253906</v>
+        <v>429.6554565429688</v>
       </c>
       <c r="C159" t="n">
         <v>439.9599914550781</v>
@@ -4584,7 +4584,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>372.486572265625</v>
+        <v>372.4866027832031</v>
       </c>
       <c r="C160" t="n">
         <v>381.4200134277344</v>
@@ -4613,7 +4613,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>368.8439025878906</v>
+        <v>368.8438720703125</v>
       </c>
       <c r="C161" t="n">
         <v>377.6900024414062</v>
